--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF1C0FBD-65A9-404E-9430-D7360636A20F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E6C8AC9-71E6-43B1-B5DF-560B095BE2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -775,13 +775,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH02,S02aH02,S01aH02,S03aH02</t>
+    <t>S04aH02,S02aH02,S03aH02,S01aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S03aH03,S04aH03,S01aH03,S02aH01,S01aH01,S04aH01,S02aH03</t>
+    <t>S01aH03,S02aH01,S01aH01,S04aH01,S03aH01,S03aH03,S02aH03,S04aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -907,10 +907,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S03aH03,S07aH05,S01aH05,S06aH05,S03aH05,S05aH05,S06aH04,S02aH04,S02aH05,S03aH04,S02aH03,S07aH03,S05aH04,S06aH03,S04aH05,S04aH03,S07aH04,S01aH03,S05aH03,S04aH04,S01aH04</t>
+    <t>S01aH04,S07aH05,S03aH04,S04aH05,S01aH05,S06aH05,S03aH05,S05aH05,S06aH04,S03aH03,S04aH03,S07aH04,S01aH03,S05aH03,S04aH04,S02aH03,S07aH03,S02aH04,S02aH05,S05aH04,S06aH03</t>
   </si>
   <si>
-    <t>S02aH02,S06aH06,S04aH02,S01aH02,S02aH06,S03aH02,S05aH01,S07aH02,S07aH06,S01aH01,S04aH01,S04aH06,S06aH02,S06aH01,S03aH01,S01aH06,S07aH01,S02aH01,S05aH02,S05aH06,S03aH06</t>
+    <t>S04aH02,S05aH01,S07aH02,S07aH06,S01aH02,S03aH01,S03aH02,S06aH01,S02aH02,S06aH06,S02aH01,S05aH02,S05aH06,S03aH06,S01aH01,S04aH01,S04aH06,S06aH02,S02aH06,S01aH06,S07aH01</t>
   </si>
   <si>
     <t>AllS</t>
@@ -976,10 +976,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,RaP,FaP,SaP,WaP,FaD,WaD,RaD</t>
+    <t>WaD,RaD,FaD,FaP,SaP,SaD,RaP,WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,FaN,RaN,RaP,WaP,SaN,WaN</t>
+    <t>FaN,RaP,SaN,WaN,WaP,FaP,SaP,RaN</t>
   </si>
 </sst>
 </file>
@@ -24640,7 +24640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{147B51EE-3BCD-4F37-A9E2-4AE2D054E680}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A50EC3-AF2E-4631-9607-F9DC49E6256C}">
   <dimension ref="A9:AN250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26828,7 +26828,7 @@
         <v>161</v>
       </c>
       <c r="AM41">
-        <v>0.14228571428571432</v>
+        <v>0.14228571428571429</v>
       </c>
       <c r="AN41" t="s">
         <v>237</v>
@@ -27428,7 +27428,7 @@
         <v>161</v>
       </c>
       <c r="AM53">
-        <v>0.14277142857142855</v>
+        <v>0.14277142857142858</v>
       </c>
       <c r="AN53" t="s">
         <v>237</v>
@@ -28028,7 +28028,7 @@
         <v>161</v>
       </c>
       <c r="AM65">
-        <v>0.19028571428571434</v>
+        <v>0.19028571428571431</v>
       </c>
       <c r="AN65" t="s">
         <v>237</v>
@@ -28228,7 +28228,7 @@
         <v>161</v>
       </c>
       <c r="AM69">
-        <v>0.19417142857142858</v>
+        <v>0.19417142857142861</v>
       </c>
       <c r="AN69" t="s">
         <v>237</v>
@@ -29028,7 +29028,7 @@
         <v>161</v>
       </c>
       <c r="AM85">
-        <v>0.17240000000000003</v>
+        <v>0.17239999999999997</v>
       </c>
       <c r="AN85" t="s">
         <v>237</v>
@@ -29228,7 +29228,7 @@
         <v>161</v>
       </c>
       <c r="AM89">
-        <v>0.17068571428571427</v>
+        <v>0.1706857142857143</v>
       </c>
       <c r="AN89" t="s">
         <v>237</v>
@@ -30228,7 +30228,7 @@
         <v>161</v>
       </c>
       <c r="AM109">
-        <v>0.13785714285714284</v>
+        <v>0.13785714285714287</v>
       </c>
       <c r="AN109" t="s">
         <v>237</v>
@@ -34362,7 +34362,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6F1E29E-EEAC-472F-82F7-415923B56F41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E9B06C-10FF-444C-9840-3464D006DE49}">
   <dimension ref="A9:AN850"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -65525,7 +65525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0E6A80D-EF86-4BC8-B660-1C69A902C227}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6833B1A7-C359-4A94-8D67-14A4A30D4821}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -65813,7 +65813,7 @@
         <v>277</v>
       </c>
       <c r="AM12">
-        <v>0.21560142735733026</v>
+        <v>0.21560142735733023</v>
       </c>
       <c r="AN12" t="s">
         <v>237</v>
@@ -65913,7 +65913,7 @@
         <v>277</v>
       </c>
       <c r="AM14">
-        <v>0.19461666666666666</v>
+        <v>0.19461666666666669</v>
       </c>
       <c r="AN14" t="s">
         <v>237</v>
@@ -66213,7 +66213,7 @@
         <v>277</v>
       </c>
       <c r="AM20">
-        <v>0.16455833333333336</v>
+        <v>0.16455833333333333</v>
       </c>
       <c r="AN20" t="s">
         <v>237</v>
@@ -66289,7 +66289,7 @@
         <v>277</v>
       </c>
       <c r="AM22">
-        <v>0.23421666666666666</v>
+        <v>0.23421666666666663</v>
       </c>
       <c r="AN22" t="s">
         <v>237</v>
@@ -66403,7 +66403,7 @@
         <v>277</v>
       </c>
       <c r="AM25">
-        <v>0.22770833333333332</v>
+        <v>0.22770833333333337</v>
       </c>
       <c r="AN25" t="s">
         <v>237</v>
@@ -66479,7 +66479,7 @@
         <v>277</v>
       </c>
       <c r="AM27">
-        <v>0.22686666666666669</v>
+        <v>0.22686666666666666</v>
       </c>
       <c r="AN27" t="s">
         <v>237</v>
@@ -66517,7 +66517,7 @@
         <v>277</v>
       </c>
       <c r="AM28">
-        <v>0.20100833333333332</v>
+        <v>0.20100833333333337</v>
       </c>
       <c r="AN28" t="s">
         <v>237</v>
@@ -66555,7 +66555,7 @@
         <v>277</v>
       </c>
       <c r="AM29">
-        <v>0.19754999999999998</v>
+        <v>0.19755</v>
       </c>
       <c r="AN29" t="s">
         <v>237</v>
@@ -66593,7 +66593,7 @@
         <v>277</v>
       </c>
       <c r="AM30">
-        <v>0.20084999999999997</v>
+        <v>0.20085</v>
       </c>
       <c r="AN30" t="s">
         <v>237</v>
@@ -66621,7 +66621,7 @@
         <v>277</v>
       </c>
       <c r="AM32">
-        <v>0.22735833333333336</v>
+        <v>0.22735833333333333</v>
       </c>
       <c r="AN32" t="s">
         <v>237</v>
@@ -66691,7 +66691,7 @@
         <v>277</v>
       </c>
       <c r="AM37">
-        <v>0.19996666666666663</v>
+        <v>0.19996666666666665</v>
       </c>
       <c r="AN37" t="s">
         <v>237</v>
@@ -66719,7 +66719,7 @@
         <v>277</v>
       </c>
       <c r="AM39">
-        <v>0.19342499999999999</v>
+        <v>0.19342500000000004</v>
       </c>
       <c r="AN39" t="s">
         <v>237</v>
@@ -66731,7 +66731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE62E569-AFAC-41CF-94F9-CCEE0CF571E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C38AC465-0F77-4999-BDC3-E7B7938D7DA2}">
   <dimension ref="A9:AN250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9051BAF3-A68B-49B3-9406-A2B16E2A2513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF1E0E2-4C34-4FBD-9527-28299EAA9EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF1E0E2-4C34-4FBD-9527-28299EAA9EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A50A8E6-61B8-4505-AA27-1EFD90C511A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,9 +434,6 @@
     <t>Pipeline gas, coal &amp; forest resources</t>
   </si>
   <si>
-    <t>1-25,36-40</t>
-  </si>
-  <si>
     <t>~tfm_ins-ts</t>
   </si>
   <si>
@@ -444,6 +441,9 @@
   </si>
   <si>
     <t>cap_bnd</t>
+  </si>
+  <si>
+    <t>1-5</t>
   </si>
 </sst>
 </file>
@@ -5739,13 +5739,13 @@
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.45">
       <c r="G1" s="15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,G1:EE1)</f>
-        <v>~Inputcell: 1-25,36-40</v>
+        <v>~Inputcell: 1-5</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.45">
@@ -7361,7 +7361,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.45">
@@ -7389,7 +7389,7 @@
         <v>35</v>
       </c>
       <c r="B84" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C84">
         <v>1.4550000000000001</v>
@@ -7401,7 +7401,7 @@
         <v>1.881</v>
       </c>
       <c r="F84" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.45">
@@ -7409,7 +7409,7 @@
         <v>32</v>
       </c>
       <c r="B85" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C85">
         <v>1.8</v>
@@ -7421,7 +7421,7 @@
         <v>3.3</v>
       </c>
       <c r="F85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565B2D61-BC92-4BB1-913F-E045539DF909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B5F6BF-3BAD-46D2-869B-25979711E87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FC9C74-A05C-4211-8443-1DCF2A434F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED3C805-2379-4797-8277-B2E00499C105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2803,7 +2803,7 @@
         <xdr:cNvPr id="30" name="Picture 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71FC97A5-455E-CAEF-F872-A462E29DEDBF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C6FF571-8F68-26C3-96BA-5D02A14F061C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4208,7 +4208,7 @@
         <xdr:cNvPr id="30" name="Picture 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7831AE09-BF89-A04F-0A3B-4FFDE2956684}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E17FB2C-F0AC-4233-D2D8-7D2F7B3EC6C0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5613,7 +5613,7 @@
         <xdr:cNvPr id="30" name="Picture 29">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFE3D289-D81B-700D-DDF3-27F8573071D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{805DA26D-0F15-1F0F-6041-4DF2891E79FD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A35A0DA-F7BB-43A2-AD19-865311453082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11D3FD9-EA5A-4B2A-94CA-B1B0D554EF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1727" uniqueCount="126">
   <si>
     <t>C1</t>
   </si>
@@ -451,6 +451,9 @@
   </si>
   <si>
     <t>HET</t>
+  </si>
+  <si>
+    <t>chp_heat_twh</t>
   </si>
 </sst>
 </file>
@@ -6269,7 +6272,7 @@
       </c>
       <c r="S12" s="22">
         <f>SUMIFS(iea_data!J3:J9999,iea_data!$B$3:$B$9999,Veda!$S$10)</f>
-        <v>65.221000000000004</v>
+        <v>50.323999999999998</v>
       </c>
       <c r="AG12">
         <v>4</v>
@@ -6968,31 +6971,31 @@
       </c>
       <c r="T23" s="24">
         <f>S12</f>
-        <v>65.221000000000004</v>
+        <v>50.323999999999998</v>
       </c>
       <c r="U23" s="25">
         <f>$S$12*J15</f>
-        <v>63.916580000000003</v>
+        <v>49.317519999999995</v>
       </c>
       <c r="V23" s="25">
         <f>$S$12*K15</f>
-        <v>62.612160000000003</v>
+        <v>48.311039999999998</v>
       </c>
       <c r="W23" s="25">
         <f t="shared" ref="W23:Z23" si="10">$S$12*L15</f>
-        <v>60.003320000000009</v>
+        <v>46.298079999999999</v>
       </c>
       <c r="X23" s="25">
         <f t="shared" si="10"/>
-        <v>54.785640000000001</v>
+        <v>42.27216</v>
       </c>
       <c r="Y23" s="25">
         <f t="shared" si="10"/>
-        <v>54.133429999999997</v>
+        <v>41.768919999999994</v>
       </c>
       <c r="Z23" s="25">
         <f t="shared" si="10"/>
-        <v>52.176800000000007</v>
+        <v>40.2592</v>
       </c>
       <c r="AA23" s="23" t="s">
         <v>17</v>
@@ -8027,7 +8030,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="10.59765625" customWidth="1"/>
@@ -8041,13 +8044,13 @@
     <col min="10" max="10" width="11.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="22.05" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -8076,10 +8079,13 @@
         <v>43</v>
       </c>
       <c r="J10" t="s">
+        <v>125</v>
+      </c>
+      <c r="K10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>118</v>
       </c>
@@ -8108,10 +8114,13 @@
         <v>143.16999999999999</v>
       </c>
       <c r="J11">
+        <v>54.661000000000001</v>
+      </c>
+      <c r="K11">
         <v>77.525000000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>118</v>
       </c>
@@ -8140,10 +8149,13 @@
         <v>143.72</v>
       </c>
       <c r="J12">
+        <v>58.131999999999998</v>
+      </c>
+      <c r="K12">
         <v>85.239000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>118</v>
       </c>
@@ -8172,10 +8184,13 @@
         <v>142.5</v>
       </c>
       <c r="J13">
+        <v>57.103000000000002</v>
+      </c>
+      <c r="K13">
         <v>80.076999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>118</v>
       </c>
@@ -8204,10 +8219,13 @@
         <v>150.01</v>
       </c>
       <c r="J14">
+        <v>62.613999999999997</v>
+      </c>
+      <c r="K14">
         <v>83.001999999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>118</v>
       </c>
@@ -8236,10 +8254,13 @@
         <v>152.55000000000001</v>
       </c>
       <c r="J15">
+        <v>60.438000000000002</v>
+      </c>
+      <c r="K15">
         <v>78.161000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>118</v>
       </c>
@@ -8268,10 +8289,13 @@
         <v>155.36000000000001</v>
       </c>
       <c r="J16">
+        <v>60.936</v>
+      </c>
+      <c r="K16">
         <v>76.881</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>118</v>
       </c>
@@ -8300,10 +8324,13 @@
         <v>160.76</v>
       </c>
       <c r="J17">
+        <v>61.061</v>
+      </c>
+      <c r="K17">
         <v>78.009</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>118</v>
       </c>
@@ -8332,10 +8359,13 @@
         <v>158.76</v>
       </c>
       <c r="J18">
+        <v>57.805</v>
+      </c>
+      <c r="K18">
         <v>72.433000000000007</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>118</v>
       </c>
@@ -8364,10 +8394,13 @@
         <v>154.71</v>
       </c>
       <c r="J19">
+        <v>55.478999999999999</v>
+      </c>
+      <c r="K19">
         <v>70.186000000000007</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>118</v>
       </c>
@@ -8396,10 +8429,13 @@
         <v>151.12</v>
       </c>
       <c r="J20">
+        <v>54.234999999999999</v>
+      </c>
+      <c r="K20">
         <v>69.751999999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>118</v>
       </c>
@@ -8428,10 +8464,13 @@
         <v>157.09</v>
       </c>
       <c r="J21">
+        <v>57.015999999999998</v>
+      </c>
+      <c r="K21">
         <v>75.994</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>118</v>
       </c>
@@ -8460,10 +8499,13 @@
         <v>163.12</v>
       </c>
       <c r="J22">
+        <v>53.280999999999999</v>
+      </c>
+      <c r="K22">
         <v>67.509</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>118</v>
       </c>
@@ -8492,10 +8534,13 @@
         <v>161.71</v>
       </c>
       <c r="J23">
+        <v>54.026000000000003</v>
+      </c>
+      <c r="K23">
         <v>69.394000000000005</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -8524,10 +8569,13 @@
         <v>164.02</v>
       </c>
       <c r="J24">
+        <v>52.933</v>
+      </c>
+      <c r="K24">
         <v>69.100999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -8556,10 +8604,13 @@
         <v>158.51</v>
       </c>
       <c r="J25">
+        <v>48.634</v>
+      </c>
+      <c r="K25">
         <v>63.122</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -8588,10 +8639,13 @@
         <v>164.34</v>
       </c>
       <c r="J26">
+        <v>51.51</v>
+      </c>
+      <c r="K26">
         <v>63.31</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>118</v>
       </c>
@@ -8620,10 +8674,13 @@
         <v>166.15</v>
       </c>
       <c r="J27">
+        <v>52.508000000000003</v>
+      </c>
+      <c r="K27">
         <v>65.72</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>118</v>
       </c>
@@ -8652,10 +8709,13 @@
         <v>169.99</v>
       </c>
       <c r="J28">
+        <v>54.637999999999998</v>
+      </c>
+      <c r="K28">
         <v>67.453000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>118</v>
       </c>
@@ -8684,10 +8744,13 @@
         <v>169.62</v>
       </c>
       <c r="J29">
+        <v>53.701000000000001</v>
+      </c>
+      <c r="K29">
         <v>64.968999999999994</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>118</v>
       </c>
@@ -8716,10 +8779,13 @@
         <v>163.28</v>
       </c>
       <c r="J30">
+        <v>52.756999999999998</v>
+      </c>
+      <c r="K30">
         <v>64.373000000000005</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>118</v>
       </c>
@@ -8748,10 +8814,13 @@
         <v>157.22</v>
       </c>
       <c r="J31">
+        <v>51.826999999999998</v>
+      </c>
+      <c r="K31">
         <v>64.936000000000007</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -8780,10 +8849,13 @@
         <v>178.87</v>
       </c>
       <c r="J32">
+        <v>54.496000000000002</v>
+      </c>
+      <c r="K32">
         <v>69.254000000000005</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>118</v>
       </c>
@@ -8812,6 +8884,9 @@
         <v>178.7</v>
       </c>
       <c r="J33">
+        <v>50.323999999999998</v>
+      </c>
+      <c r="K33">
         <v>65.221000000000004</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C11D3FD9-EA5A-4B2A-94CA-B1B0D554EF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6494C6-CC9D-489A-84D8-14BAE83D3229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6494C6-CC9D-489A-84D8-14BAE83D3229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C61D1D-AB98-45A1-9543-0F6BF84AC29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C61D1D-AB98-45A1-9543-0F6BF84AC29D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEDC3EE-2E2A-411D-B35A-5D9CE442410B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,9 +438,6 @@
     <t>Pipeline gas, coal &amp; forest resources</t>
   </si>
   <si>
-    <t>1-25,36-40</t>
-  </si>
-  <si>
     <t>~tfm_ins-ts</t>
   </si>
   <si>
@@ -451,6 +448,9 @@
   </si>
   <si>
     <t>HET</t>
+  </si>
+  <si>
+    <t>1-8</t>
   </si>
   <si>
     <t>chp_heat_twh</t>
@@ -6022,13 +6022,13 @@
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.45">
       <c r="G1" s="21" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.45">
       <c r="D2" s="1" t="str">
         <f>"~Inputcell: "&amp;_xlfn.TEXTJOIN(",",TRUE,G1:EE1)</f>
-        <v>~Inputcell: 1-25,36-40</v>
+        <v>~Inputcell: 1-8</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>26</v>
@@ -6967,7 +6967,7 @@
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.45">
       <c r="S23" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T23" s="24">
         <f>S12</f>
@@ -7805,7 +7805,7 @@
     </row>
     <row r="82" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A82" s="12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.6">
@@ -7833,7 +7833,7 @@
         <v>34</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C84" s="18">
         <v>1.4550000000000001</v>
@@ -7845,7 +7845,7 @@
         <v>1.881</v>
       </c>
       <c r="F84" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.45">
@@ -7853,7 +7853,7 @@
         <v>31</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C85" s="20">
         <v>1.8</v>
@@ -7865,12 +7865,12 @@
         <v>3.3</v>
       </c>
       <c r="F85" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.45">
@@ -7898,7 +7898,7 @@
         <v>34</v>
       </c>
       <c r="B91" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C91">
         <v>1.4550000000000001</v>
@@ -7910,7 +7910,7 @@
         <v>1.881</v>
       </c>
       <c r="F91" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.45">
@@ -7918,7 +7918,7 @@
         <v>31</v>
       </c>
       <c r="B92" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92">
         <v>1.8</v>
@@ -7930,7 +7930,7 @@
         <v>3.3</v>
       </c>
       <c r="F92" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -19055,8 +19055,8 @@
       <c r="D257">
         <v>34</v>
       </c>
-      <c r="E257">
-        <v>65535</v>
+      <c r="E257" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F257">
         <v>2.42</v>
@@ -19064,8 +19064,8 @@
       <c r="H257">
         <v>1.18</v>
       </c>
-      <c r="I257">
-        <v>65535</v>
+      <c r="I257" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J257">
         <v>2.0099999999999998</v>
@@ -19093,8 +19093,8 @@
       <c r="D258">
         <v>34</v>
       </c>
-      <c r="E258">
-        <v>65535</v>
+      <c r="E258" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F258">
         <v>3.1</v>
@@ -19102,8 +19102,8 @@
       <c r="H258">
         <v>1.71</v>
       </c>
-      <c r="I258">
-        <v>65535</v>
+      <c r="I258" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J258">
         <v>2.38</v>
@@ -19131,8 +19131,8 @@
       <c r="D259">
         <v>34</v>
       </c>
-      <c r="E259">
-        <v>65535</v>
+      <c r="E259" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F259">
         <v>3.54</v>
@@ -19140,8 +19140,8 @@
       <c r="H259">
         <v>1.91</v>
       </c>
-      <c r="I259">
-        <v>65535</v>
+      <c r="I259" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J259">
         <v>2.66</v>
@@ -19169,8 +19169,8 @@
       <c r="D260">
         <v>34</v>
       </c>
-      <c r="E260">
-        <v>65535</v>
+      <c r="E260" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F260">
         <v>4.0999999999999996</v>
@@ -19178,8 +19178,8 @@
       <c r="H260">
         <v>2.27</v>
       </c>
-      <c r="I260">
-        <v>65535</v>
+      <c r="I260" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J260">
         <v>2.96</v>
@@ -19207,8 +19207,8 @@
       <c r="D261">
         <v>34</v>
       </c>
-      <c r="E261">
-        <v>65535</v>
+      <c r="E261" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F261">
         <v>3.86</v>
@@ -19216,8 +19216,8 @@
       <c r="H261">
         <v>2.54</v>
       </c>
-      <c r="I261">
-        <v>65535</v>
+      <c r="I261" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J261">
         <v>3.3</v>
@@ -19245,8 +19245,8 @@
       <c r="D262">
         <v>34</v>
       </c>
-      <c r="E262">
-        <v>65535</v>
+      <c r="E262" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F262">
         <v>3.59</v>
@@ -19254,8 +19254,8 @@
       <c r="H262">
         <v>2.73</v>
       </c>
-      <c r="I262">
-        <v>65535</v>
+      <c r="I262" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J262">
         <v>3.07</v>
@@ -19324,8 +19324,8 @@
       <c r="D264">
         <v>44</v>
       </c>
-      <c r="E264">
-        <v>65535</v>
+      <c r="E264" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F264">
         <v>1.22</v>
@@ -19333,8 +19333,8 @@
       <c r="H264">
         <v>0</v>
       </c>
-      <c r="I264">
-        <v>65535</v>
+      <c r="I264" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J264">
         <v>1.1299999999999999</v>
@@ -19362,8 +19362,8 @@
       <c r="D265">
         <v>44</v>
       </c>
-      <c r="E265">
-        <v>65535</v>
+      <c r="E265" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F265">
         <v>1.5</v>
@@ -19371,8 +19371,8 @@
       <c r="H265">
         <v>0</v>
       </c>
-      <c r="I265">
-        <v>65535</v>
+      <c r="I265" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J265">
         <v>1.31</v>
@@ -19400,8 +19400,8 @@
       <c r="D266">
         <v>44</v>
       </c>
-      <c r="E266">
-        <v>65535</v>
+      <c r="E266" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F266">
         <v>2.12</v>
@@ -19409,8 +19409,8 @@
       <c r="H266">
         <v>0</v>
       </c>
-      <c r="I266">
-        <v>65535</v>
+      <c r="I266" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J266">
         <v>1.68</v>
@@ -19438,8 +19438,8 @@
       <c r="D267">
         <v>44</v>
       </c>
-      <c r="E267">
-        <v>65535</v>
+      <c r="E267" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F267">
         <v>2.5</v>
@@ -19447,8 +19447,8 @@
       <c r="H267">
         <v>0</v>
       </c>
-      <c r="I267">
-        <v>65535</v>
+      <c r="I267" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J267">
         <v>2</v>
@@ -19476,8 +19476,8 @@
       <c r="D268">
         <v>44</v>
       </c>
-      <c r="E268">
-        <v>65535</v>
+      <c r="E268" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F268">
         <v>2.79</v>
@@ -19485,8 +19485,8 @@
       <c r="H268">
         <v>0</v>
       </c>
-      <c r="I268">
-        <v>65535</v>
+      <c r="I268" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J268">
         <v>2.08</v>
@@ -19514,8 +19514,8 @@
       <c r="D269">
         <v>44</v>
       </c>
-      <c r="E269">
-        <v>65535</v>
+      <c r="E269" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F269">
         <v>2.95</v>
@@ -19523,8 +19523,8 @@
       <c r="H269">
         <v>0</v>
       </c>
-      <c r="I269">
-        <v>65535</v>
+      <c r="I269" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J269">
         <v>2.4900000000000002</v>
@@ -19593,8 +19593,8 @@
       <c r="D271">
         <v>112</v>
       </c>
-      <c r="E271">
-        <v>65535</v>
+      <c r="E271" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F271">
         <v>1.41</v>
@@ -19602,8 +19602,8 @@
       <c r="H271">
         <v>0.98</v>
       </c>
-      <c r="I271">
-        <v>65535</v>
+      <c r="I271" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J271">
         <v>1.23</v>
@@ -19631,8 +19631,8 @@
       <c r="D272">
         <v>112</v>
       </c>
-      <c r="E272">
-        <v>65535</v>
+      <c r="E272" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F272">
         <v>2.04</v>
@@ -19640,8 +19640,8 @@
       <c r="H272">
         <v>1.05</v>
       </c>
-      <c r="I272">
-        <v>65535</v>
+      <c r="I272" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J272">
         <v>1.52</v>
@@ -19669,8 +19669,8 @@
       <c r="D273">
         <v>112</v>
       </c>
-      <c r="E273">
-        <v>65535</v>
+      <c r="E273" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F273">
         <v>2.4</v>
@@ -19678,8 +19678,8 @@
       <c r="H273">
         <v>1.05</v>
       </c>
-      <c r="I273">
-        <v>65535</v>
+      <c r="I273" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J273">
         <v>1.71</v>
@@ -19707,8 +19707,8 @@
       <c r="D274">
         <v>112</v>
       </c>
-      <c r="E274">
-        <v>65535</v>
+      <c r="E274" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F274">
         <v>2.6</v>
@@ -19716,8 +19716,8 @@
       <c r="H274">
         <v>1.06</v>
       </c>
-      <c r="I274">
-        <v>65535</v>
+      <c r="I274" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J274">
         <v>1.85</v>
@@ -19745,8 +19745,8 @@
       <c r="D275">
         <v>112</v>
       </c>
-      <c r="E275">
-        <v>65535</v>
+      <c r="E275" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F275">
         <v>2.85</v>
@@ -19754,8 +19754,8 @@
       <c r="H275">
         <v>1.08</v>
       </c>
-      <c r="I275">
-        <v>65535</v>
+      <c r="I275" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J275">
         <v>2</v>
@@ -19783,8 +19783,8 @@
       <c r="D276">
         <v>112</v>
       </c>
-      <c r="E276">
-        <v>65535</v>
+      <c r="E276" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F276">
         <v>2.97</v>
@@ -19792,8 +19792,8 @@
       <c r="H276">
         <v>0</v>
       </c>
-      <c r="I276">
-        <v>65535</v>
+      <c r="I276" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J276">
         <v>2.15</v>
@@ -20436,8 +20436,8 @@
       <c r="D292">
         <v>50</v>
       </c>
-      <c r="E292">
-        <v>65535</v>
+      <c r="E292" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F292">
         <v>1.1000000000000001</v>
@@ -20445,8 +20445,8 @@
       <c r="H292">
         <v>-4.33</v>
       </c>
-      <c r="I292">
-        <v>65535</v>
+      <c r="I292" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J292">
         <v>0.81</v>
@@ -20474,8 +20474,8 @@
       <c r="D293">
         <v>50</v>
       </c>
-      <c r="E293">
-        <v>65535</v>
+      <c r="E293" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F293">
         <v>1.77</v>
@@ -20483,8 +20483,8 @@
       <c r="H293">
         <v>-6.1</v>
       </c>
-      <c r="I293">
-        <v>65535</v>
+      <c r="I293" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J293">
         <v>1.27</v>
@@ -20512,8 +20512,8 @@
       <c r="D294">
         <v>50</v>
       </c>
-      <c r="E294">
-        <v>65535</v>
+      <c r="E294" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F294">
         <v>1.87</v>
@@ -20521,8 +20521,8 @@
       <c r="H294">
         <v>-6.86</v>
       </c>
-      <c r="I294">
-        <v>65535</v>
+      <c r="I294" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J294">
         <v>1.1499999999999999</v>
@@ -20550,8 +20550,8 @@
       <c r="D295">
         <v>50</v>
       </c>
-      <c r="E295">
-        <v>65535</v>
+      <c r="E295" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F295">
         <v>1.96</v>
@@ -20559,8 +20559,8 @@
       <c r="H295">
         <v>-9.2100000000000009</v>
       </c>
-      <c r="I295">
-        <v>65535</v>
+      <c r="I295" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J295">
         <v>1.31</v>
@@ -20588,8 +20588,8 @@
       <c r="D296">
         <v>50</v>
       </c>
-      <c r="E296">
-        <v>65535</v>
+      <c r="E296" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F296">
         <v>2.13</v>
@@ -20597,8 +20597,8 @@
       <c r="H296">
         <v>-6.95</v>
       </c>
-      <c r="I296">
-        <v>65535</v>
+      <c r="I296" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J296">
         <v>1.6</v>
@@ -20626,8 +20626,8 @@
       <c r="D297">
         <v>50</v>
       </c>
-      <c r="E297">
-        <v>65535</v>
+      <c r="E297" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F297">
         <v>2</v>
@@ -20635,8 +20635,8 @@
       <c r="H297">
         <v>-10.07</v>
       </c>
-      <c r="I297">
-        <v>65535</v>
+      <c r="I297" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J297">
         <v>1.55</v>
@@ -20705,8 +20705,8 @@
       <c r="D299">
         <v>52</v>
       </c>
-      <c r="E299">
-        <v>65535</v>
+      <c r="E299" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F299">
         <v>0.61</v>
@@ -20714,8 +20714,8 @@
       <c r="H299">
         <v>0</v>
       </c>
-      <c r="I299">
-        <v>65535</v>
+      <c r="I299" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J299">
         <v>0.53</v>
@@ -20743,8 +20743,8 @@
       <c r="D300">
         <v>63</v>
       </c>
-      <c r="E300">
-        <v>65535</v>
+      <c r="E300" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F300">
         <v>1.07</v>
@@ -20752,8 +20752,8 @@
       <c r="H300">
         <v>0</v>
       </c>
-      <c r="I300">
-        <v>65535</v>
+      <c r="I300" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J300">
         <v>0.6</v>
@@ -20781,8 +20781,8 @@
       <c r="D301">
         <v>52</v>
       </c>
-      <c r="E301">
-        <v>65535</v>
+      <c r="E301" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F301">
         <v>1.0900000000000001</v>
@@ -20790,8 +20790,8 @@
       <c r="H301">
         <v>0</v>
       </c>
-      <c r="I301">
-        <v>65535</v>
+      <c r="I301" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J301">
         <v>0.6</v>
@@ -20819,8 +20819,8 @@
       <c r="D302">
         <v>63</v>
       </c>
-      <c r="E302">
-        <v>65535</v>
+      <c r="E302" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F302">
         <v>1.25</v>
@@ -20828,8 +20828,8 @@
       <c r="H302">
         <v>0</v>
       </c>
-      <c r="I302">
-        <v>65535</v>
+      <c r="I302" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J302">
         <v>0.87</v>
@@ -20857,8 +20857,8 @@
       <c r="D303">
         <v>52</v>
       </c>
-      <c r="E303">
-        <v>65535</v>
+      <c r="E303" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F303">
         <v>1.35</v>
@@ -20866,8 +20866,8 @@
       <c r="H303">
         <v>0</v>
       </c>
-      <c r="I303">
-        <v>65535</v>
+      <c r="I303" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J303">
         <v>0.78</v>
@@ -20895,8 +20895,8 @@
       <c r="D304">
         <v>63</v>
       </c>
-      <c r="E304">
-        <v>65535</v>
+      <c r="E304" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F304">
         <v>1.62</v>
@@ -20904,8 +20904,8 @@
       <c r="H304">
         <v>-2.31</v>
       </c>
-      <c r="I304">
-        <v>65535</v>
+      <c r="I304" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J304">
         <v>0.61</v>
@@ -20974,8 +20974,8 @@
       <c r="D306">
         <v>163</v>
       </c>
-      <c r="E306">
-        <v>65535</v>
+      <c r="E306" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F306">
         <v>0.75</v>
@@ -20983,8 +20983,8 @@
       <c r="H306">
         <v>0.46</v>
       </c>
-      <c r="I306">
-        <v>65535</v>
+      <c r="I306" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J306">
         <v>0.54</v>
@@ -21012,8 +21012,8 @@
       <c r="D307">
         <v>166</v>
       </c>
-      <c r="E307">
-        <v>65535</v>
+      <c r="E307" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F307">
         <v>1.1499999999999999</v>
@@ -21021,8 +21021,8 @@
       <c r="H307">
         <v>0.51</v>
       </c>
-      <c r="I307">
-        <v>65535</v>
+      <c r="I307" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J307">
         <v>0.74</v>
@@ -21050,8 +21050,8 @@
       <c r="D308">
         <v>163</v>
       </c>
-      <c r="E308">
-        <v>65535</v>
+      <c r="E308" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F308">
         <v>1.21</v>
@@ -21059,8 +21059,8 @@
       <c r="H308">
         <v>-0.95</v>
       </c>
-      <c r="I308">
-        <v>65535</v>
+      <c r="I308" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J308">
         <v>0.88</v>
@@ -21088,8 +21088,8 @@
       <c r="D309">
         <v>166</v>
       </c>
-      <c r="E309">
-        <v>65535</v>
+      <c r="E309" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F309">
         <v>1.28</v>
@@ -21097,8 +21097,8 @@
       <c r="H309">
         <v>-1.8</v>
       </c>
-      <c r="I309">
-        <v>65535</v>
+      <c r="I309" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J309">
         <v>0.89</v>
@@ -21126,8 +21126,8 @@
       <c r="D310">
         <v>163</v>
       </c>
-      <c r="E310">
-        <v>65535</v>
+      <c r="E310" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F310">
         <v>1.48</v>
@@ -21135,8 +21135,8 @@
       <c r="H310">
         <v>-5.93</v>
       </c>
-      <c r="I310">
-        <v>65535</v>
+      <c r="I310" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J310">
         <v>1.08</v>
@@ -21164,8 +21164,8 @@
       <c r="D311">
         <v>166</v>
       </c>
-      <c r="E311">
-        <v>65535</v>
+      <c r="E311" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F311">
         <v>1.59</v>
@@ -21173,8 +21173,8 @@
       <c r="H311">
         <v>-5.35</v>
       </c>
-      <c r="I311">
-        <v>65535</v>
+      <c r="I311" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J311">
         <v>0.97</v>
